--- a/.agents/outputs/vb-payables-preview/three-category-example.xlsx
+++ b/.agents/outputs/vb-payables-preview/three-category-example.xlsx
@@ -438,7 +438,7 @@
         <v>Generated</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-10-04T16:52:52.578Z</v>
+        <v>2026-10-04T17:12:24.505Z</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         <v>Generated</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-04T16:52:52.578Z</v>
+        <v>2026-10-04T17:12:24.505Z</v>
       </c>
     </row>
     <row r="3">
@@ -2128,7 +2128,7 @@
         <v>Generated</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-04T16:52:52.578Z</v>
+        <v>2026-10-04T17:12:24.505Z</v>
       </c>
     </row>
     <row r="3">
@@ -2246,7 +2246,7 @@
         <v>Generated</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-04T16:52:52.578Z</v>
+        <v>2026-10-04T17:12:24.505Z</v>
       </c>
     </row>
     <row r="3">
@@ -2335,7 +2335,7 @@
         <v>Generated</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-04T16:52:52.578Z</v>
+        <v>2026-10-04T17:12:24.505Z</v>
       </c>
     </row>
     <row r="3">
@@ -2453,7 +2453,7 @@
         <v>Generated</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-10-04T16:52:52.578Z</v>
+        <v>2026-10-04T17:12:24.505Z</v>
       </c>
     </row>
     <row r="3">
